--- a/mentor data/haider 8-talaria-adapted.xlsx
+++ b/mentor data/haider 8-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49407, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "exitScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49407, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "exitScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33718, "sourceLowPrice": 1.33432}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK2" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782553948995</v>
+        <v>1782575547415</v>
       </c>
       <c r="BM2" t="n">
         <v>1.33374</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49408, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "exitScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49408, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "exitScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33661, "sourceLowPrice": 1.33377}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK3" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782553948996</v>
+        <v>1782575547416</v>
       </c>
       <c r="BM3" t="n">
         <v>1.33277</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49409, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "exitScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49409, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "exitScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33868, "sourceLowPrice": 1.33594}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK4" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782553948996</v>
+        <v>1782575547417</v>
       </c>
       <c r="BM4" t="n">
         <v>1.33741</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49411, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "exitScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49411, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "exitScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34019, "sourceLowPrice": 1.33606}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK5" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782553948996</v>
+        <v>1782575547417</v>
       </c>
       <c r="BM5" t="n">
         <v>1.33501</v>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49413, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "exitScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49413, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "exitScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33908, "sourceLowPrice": 1.3357}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK6" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782553948996</v>
+        <v>1782575547418</v>
       </c>
       <c r="BM6" t="n">
         <v>1.33924</v>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49414, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "exitScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49414, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "exitScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33714, "sourceLowPrice": 1.33506}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK7" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782553948997</v>
+        <v>1782575547418</v>
       </c>
       <c r="BM7" t="n">
         <v>1.338</v>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49415, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "exitScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49415, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "exitScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33866, "sourceLowPrice": 1.33434}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK8" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782553948997</v>
+        <v>1782575547419</v>
       </c>
       <c r="BM8" t="n">
         <v>1.33873</v>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49416, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "exitScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49416, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "exitScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34403, "sourceLowPrice": 1.3413}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK9" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782553948997</v>
+        <v>1782575547419</v>
       </c>
       <c r="BM9" t="n">
         <v>1.3408</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49417, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "exitScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49417, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "exitScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34777, "sourceLowPrice": 1.34452}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK10" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782553948997</v>
+        <v>1782575547419</v>
       </c>
       <c r="BM10" t="n">
         <v>1.34696</v>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="DQ10" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR10" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS10" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49418, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "exitScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49418, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "exitScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35019, "sourceLowPrice": 1.3457}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6069,13 +6069,13 @@
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK11" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782553948997</v>
+        <v>1782575547420</v>
       </c>
       <c r="BM11" t="n">
         <v>1.34425</v>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49419, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "exitScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49419, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "exitScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35358, "sourceLowPrice": 1.35056}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6593,13 +6593,13 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK12" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782553948998</v>
+        <v>1782575547420</v>
       </c>
       <c r="BM12" t="n">
         <v>1.35019</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS12" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49420, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49420, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35272, "sourceLowPrice": 1.34827}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="BJ13" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK13" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782553948998</v>
+        <v>1782575547421</v>
       </c>
       <c r="BM13" t="n">
         <v>1.34802</v>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS13" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49421, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "exitScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49421, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "exitScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34868, "sourceLowPrice": 1.34402}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK14" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782553948998</v>
+        <v>1782575547422</v>
       </c>
       <c r="BM14" t="n">
         <v>1.34969</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS14" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49422, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49422, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34586, "sourceLowPrice": 1.3426}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK15" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782553948998</v>
+        <v>1782575547422</v>
       </c>
       <c r="BM15" t="n">
         <v>1.34502</v>
@@ -8373,12 +8373,12 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS15" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49468, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "exitScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49468, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "exitScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3492, "sourceLowPrice": 1.3467}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK16" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782553948998</v>
+        <v>1782575547423</v>
       </c>
       <c r="BM16" t="n">
         <v>1.34627</v>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS16" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49469, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49469, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35162, "sourceLowPrice": 1.34733}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="BJ17" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK17" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782553948999</v>
+        <v>1782575547423</v>
       </c>
       <c r="BM17" t="n">
         <v>1.34689</v>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS17" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49470, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "exitScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49470, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "exitScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35192, "sourceLowPrice": 1.34855}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9737,13 +9737,13 @@
         </is>
       </c>
       <c r="BJ18" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK18" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782553948999</v>
+        <v>1782575547424</v>
       </c>
       <c r="BM18" t="n">
         <v>1.34981</v>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR18" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49471, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "exitScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49471, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "exitScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34547, "sourceLowPrice": 1.34352}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10261,13 +10261,13 @@
         </is>
       </c>
       <c r="BJ19" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK19" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782553948999</v>
+        <v>1782575547425</v>
       </c>
       <c r="BM19" t="n">
         <v>1.34446</v>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR19" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS19" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49472, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "exitScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49472, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "exitScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34466, "sourceLowPrice": 1.34302}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="BJ20" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK20" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782553948999</v>
+        <v>1782575547425</v>
       </c>
       <c r="BM20" t="n">
         <v>1.3441</v>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR20" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS20" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49473, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "exitScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49473, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "exitScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34372, "sourceLowPrice": 1.34008}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="BJ21" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK21" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782553948999</v>
+        <v>1782575547425</v>
       </c>
       <c r="BM21" t="n">
         <v>1.34492</v>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR21" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS21" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49474, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49474, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34478, "sourceLowPrice": 1.34124}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="BJ22" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK22" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782553949000</v>
+        <v>1782575547426</v>
       </c>
       <c r="BM22" t="n">
         <v>1.34562</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="DQ22" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR22" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS22" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49477, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "exitScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49477, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "exitScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27952, "sourceLowPrice": 1.27554}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12357,13 +12357,13 @@
         </is>
       </c>
       <c r="BJ23" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK23" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782553949000</v>
+        <v>1782575547426</v>
       </c>
       <c r="BM23" t="n">
         <v>1.2798</v>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="DQ23" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR23" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS23" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49490, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "exitScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49490, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "exitScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35433, "sourceLowPrice": 1.35118}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12881,13 +12881,13 @@
         </is>
       </c>
       <c r="BJ24" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK24" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782553949000</v>
+        <v>1782575547426</v>
       </c>
       <c r="BM24" t="n">
         <v>1.35455</v>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="DQ24" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR24" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS24" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49491, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "exitScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49491, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "exitScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34807, "sourceLowPrice": 1.3455}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13405,13 +13405,13 @@
         </is>
       </c>
       <c r="BJ25" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK25" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782553949000</v>
+        <v>1782575547427</v>
       </c>
       <c r="BM25" t="n">
         <v>1.34881</v>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="DQ25" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR25" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49492, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "exitScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49492, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "exitScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3469, "sourceLowPrice": 1.34524}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13929,13 +13929,13 @@
         </is>
       </c>
       <c r="BJ26" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK26" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782553949000</v>
+        <v>1782575547427</v>
       </c>
       <c r="BM26" t="n">
         <v>1.34575</v>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="DQ26" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR26" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS26" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49493, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "exitScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49493, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "exitScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34818, "sourceLowPrice": 1.34311}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14453,13 +14453,13 @@
         </is>
       </c>
       <c r="BJ27" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK27" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782553949001</v>
+        <v>1782575547428</v>
       </c>
       <c r="BM27" t="n">
         <v>1.34289</v>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="DQ27" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR27" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS27" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49494, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "exitScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49494, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "exitScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35076, "sourceLowPrice": 1.34759}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14977,13 +14977,13 @@
         </is>
       </c>
       <c r="BJ28" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK28" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782553949001</v>
+        <v>1782575547428</v>
       </c>
       <c r="BM28" t="n">
         <v>1.34694</v>
@@ -15185,12 +15185,12 @@
       </c>
       <c r="DQ28" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR28" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS28" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49495, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "exitScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49495, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "exitScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3526, "sourceLowPrice": 1.35139}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="BJ29" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK29" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782553949001</v>
+        <v>1782575547429</v>
       </c>
       <c r="BM29" t="n">
         <v>1.35174</v>
@@ -15709,12 +15709,12 @@
       </c>
       <c r="DQ29" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR29" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49496, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "exitScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49496, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "exitScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35236, "sourceLowPrice": 1.35056}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16025,13 +16025,13 @@
         </is>
       </c>
       <c r="BJ30" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK30" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782553949001</v>
+        <v>1782575547429</v>
       </c>
       <c r="BM30" t="n">
         <v>1.35116</v>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="DQ30" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR30" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS30" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49497, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "exitScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49497, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "exitScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35, "sourceLowPrice": 1.34682}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16549,13 +16549,13 @@
         </is>
       </c>
       <c r="BJ31" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK31" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782553949001</v>
+        <v>1782575547430</v>
       </c>
       <c r="BM31" t="n">
         <v>1.34593</v>
@@ -16757,12 +16757,12 @@
       </c>
       <c r="DQ31" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR31" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49498, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "exitScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49498, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "exitScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35191, "sourceLowPrice": 1.35014}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17073,13 +17073,13 @@
         </is>
       </c>
       <c r="BJ32" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK32" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782553949002</v>
+        <v>1782575547430</v>
       </c>
       <c r="BM32" t="n">
         <v>1.35106</v>
@@ -17281,12 +17281,12 @@
       </c>
       <c r="DQ32" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR32" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS32" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49499, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "exitScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49499, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "exitScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35331, "sourceLowPrice": 1.34914}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17597,13 +17597,13 @@
         </is>
       </c>
       <c r="BJ33" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK33" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782553949002</v>
+        <v>1782575547431</v>
       </c>
       <c r="BM33" t="n">
         <v>1.34827</v>
@@ -17805,12 +17805,12 @@
       </c>
       <c r="DQ33" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR33" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS33" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49508, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "exitScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49508, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "exitScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35638, "sourceLowPrice": 1.35411}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="BJ34" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK34" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782553949002</v>
+        <v>1782575547431</v>
       </c>
       <c r="BM34" t="n">
         <v>1.35505</v>
@@ -18329,12 +18329,12 @@
       </c>
       <c r="DQ34" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR34" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS34" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49509, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "exitScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49509, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "exitScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35852, "sourceLowPrice": 1.35502}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18645,13 +18645,13 @@
         </is>
       </c>
       <c r="BJ35" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK35" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782553949002</v>
+        <v>1782575547431</v>
       </c>
       <c r="BM35" t="n">
         <v>1.35387</v>
@@ -18853,12 +18853,12 @@
       </c>
       <c r="DQ35" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR35" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS35" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49510, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "exitScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49510, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "exitScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36018, "sourceLowPrice": 1.35717}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="BJ36" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK36" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782553949002</v>
+        <v>1782575547432</v>
       </c>
       <c r="BM36" t="n">
         <v>1.3567</v>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="DQ36" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR36" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS36" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49511, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "exitScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49511, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "exitScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35837, "sourceLowPrice": 1.35614}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19693,13 +19693,13 @@
         </is>
       </c>
       <c r="BJ37" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK37" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782553949003</v>
+        <v>1782575547432</v>
       </c>
       <c r="BM37" t="n">
         <v>1.35561</v>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="DQ37" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR37" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS37" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49512, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "exitScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49512, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "exitScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35854, "sourceLowPrice": 1.35732}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20217,13 +20217,13 @@
         </is>
       </c>
       <c r="BJ38" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK38" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782553949003</v>
+        <v>1782575547432</v>
       </c>
       <c r="BM38" t="n">
         <v>1.35772</v>
@@ -20425,12 +20425,12 @@
       </c>
       <c r="DQ38" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR38" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS38" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49513, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "exitScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49513, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "exitScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35784, "sourceLowPrice": 1.35561}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20741,13 +20741,13 @@
         </is>
       </c>
       <c r="BJ39" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK39" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782553949003</v>
+        <v>1782575547433</v>
       </c>
       <c r="BM39" t="n">
         <v>1.35684</v>
@@ -20949,12 +20949,12 @@
       </c>
       <c r="DQ39" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR39" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS39" t="inlineStr">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49514, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "exitScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49514, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "exitScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34914, "sourceLowPrice": 1.34712}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21265,13 +21265,13 @@
         </is>
       </c>
       <c r="BJ40" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK40" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782553949003</v>
+        <v>1782575547433</v>
       </c>
       <c r="BM40" t="n">
         <v>1.34799</v>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="DQ40" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR40" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS40" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49515, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "exitScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49515, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "exitScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34944, "sourceLowPrice": 1.34661}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21789,13 +21789,13 @@
         </is>
       </c>
       <c r="BJ41" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK41" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782553949003</v>
+        <v>1782575547434</v>
       </c>
       <c r="BM41" t="n">
         <v>1.34999</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="DQ41" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR41" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS41" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49517, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49517, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35514, "sourceLowPrice": 1.35128}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22313,13 +22313,13 @@
         </is>
       </c>
       <c r="BJ42" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK42" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782553949003</v>
+        <v>1782575547434</v>
       </c>
       <c r="BM42" t="n">
         <v>1.35072</v>
@@ -22521,12 +22521,12 @@
       </c>
       <c r="DQ42" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR42" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS42" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49518, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "exitScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49518, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "exitScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35518, "sourceLowPrice": 1.3531}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22837,13 +22837,13 @@
         </is>
       </c>
       <c r="BJ43" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK43" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782553949004</v>
+        <v>1782575547435</v>
       </c>
       <c r="BM43" t="n">
         <v>1.35485</v>
@@ -23045,12 +23045,12 @@
       </c>
       <c r="DQ43" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR43" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS43" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49519, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "exitScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49519, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "exitScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35912, "sourceLowPrice": 1.35754}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23361,13 +23361,13 @@
         </is>
       </c>
       <c r="BJ44" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK44" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782553949004</v>
+        <v>1782575547435</v>
       </c>
       <c r="BM44" t="n">
         <v>1.35812</v>
@@ -23569,12 +23569,12 @@
       </c>
       <c r="DQ44" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR44" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS44" t="inlineStr">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49520, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "exitScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49520, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "exitScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35419, "sourceLowPrice": 1.35054}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23885,13 +23885,13 @@
         </is>
       </c>
       <c r="BJ45" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK45" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782553949004</v>
+        <v>1782575547436</v>
       </c>
       <c r="BM45" t="n">
         <v>1.34948</v>
@@ -24093,12 +24093,12 @@
       </c>
       <c r="DQ45" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR45" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS45" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49521, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49521, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24409,13 +24409,13 @@
         </is>
       </c>
       <c r="BJ46" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK46" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782553949004</v>
+        <v>1782575547437</v>
       </c>
       <c r="BM46" t="n">
         <v>1.356</v>
@@ -24617,12 +24617,12 @@
       </c>
       <c r="DQ46" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR46" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS46" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49522, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49522, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24933,13 +24933,13 @@
         </is>
       </c>
       <c r="BJ47" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK47" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782553949004</v>
+        <v>1782575547436</v>
       </c>
       <c r="BM47" t="n">
         <v>1.356</v>
@@ -25141,12 +25141,12 @@
       </c>
       <c r="DQ47" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR47" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS47" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49523, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49523, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35762}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25457,13 +25457,13 @@
         </is>
       </c>
       <c r="BJ48" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK48" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782553949005</v>
+        <v>1782575547437</v>
       </c>
       <c r="BM48" t="n">
         <v>1.35851</v>
@@ -25665,12 +25665,12 @@
       </c>
       <c r="DQ48" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR48" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS48" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49524, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "exitScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49524, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "exitScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35822, "sourceLowPrice": 1.35611}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25981,13 +25981,13 @@
         </is>
       </c>
       <c r="BJ49" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK49" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782553949005</v>
+        <v>1782575547438</v>
       </c>
       <c r="BM49" t="n">
         <v>1.35678</v>
@@ -26189,12 +26189,12 @@
       </c>
       <c r="DQ49" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR49" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS49" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49525, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "exitScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49525, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "exitScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35856, "sourceLowPrice": 1.35682}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26505,13 +26505,13 @@
         </is>
       </c>
       <c r="BJ50" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK50" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782553949005</v>
+        <v>1782575547439</v>
       </c>
       <c r="BM50" t="n">
         <v>1.35798</v>
@@ -26713,12 +26713,12 @@
       </c>
       <c r="DQ50" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR50" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS50" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49526, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "exitScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49526, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "exitScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3595, "sourceLowPrice": 1.35769}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27029,13 +27029,13 @@
         </is>
       </c>
       <c r="BJ51" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK51" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782553949006</v>
+        <v>1782575547439</v>
       </c>
       <c r="BM51" t="n">
         <v>1.35865</v>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="DQ51" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR51" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS51" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49527, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "exitScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49527, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "exitScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35849, "sourceLowPrice": 1.35558}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="BJ52" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK52" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782553949006</v>
+        <v>1782575547440</v>
       </c>
       <c r="BM52" t="n">
         <v>1.35425</v>
@@ -27761,12 +27761,12 @@
       </c>
       <c r="DQ52" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR52" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS52" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49528, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49528, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35696, "sourceLowPrice": 1.35494}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28077,13 +28077,13 @@
         </is>
       </c>
       <c r="BJ53" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK53" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782553949006</v>
+        <v>1782575547440</v>
       </c>
       <c r="BM53" t="n">
         <v>1.35603</v>
@@ -28285,12 +28285,12 @@
       </c>
       <c r="DQ53" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR53" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS53" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49529, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "exitScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49529, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "exitScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36086, "sourceLowPrice": 1.35546}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28601,13 +28601,13 @@
         </is>
       </c>
       <c r="BJ54" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK54" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782553949006</v>
+        <v>1782575547440</v>
       </c>
       <c r="BM54" t="n">
         <v>1.35476</v>
@@ -28809,12 +28809,12 @@
       </c>
       <c r="DQ54" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR54" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS54" t="inlineStr">
@@ -29076,7 +29076,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49530, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "exitScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49530, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "exitScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35694}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29125,13 +29125,13 @@
         </is>
       </c>
       <c r="BJ55" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK55" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782553949006</v>
+        <v>1782575547441</v>
       </c>
       <c r="BM55" t="n">
         <v>1.35841</v>
@@ -29333,12 +29333,12 @@
       </c>
       <c r="DQ55" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR55" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS55" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49531, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49531, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35999, "sourceLowPrice": 1.3577}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="BJ56" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK56" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782553949007</v>
+        <v>1782575547441</v>
       </c>
       <c r="BM56" t="n">
         <v>1.3567</v>
@@ -29857,12 +29857,12 @@
       </c>
       <c r="DQ56" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR56" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS56" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49532, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "exitScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49532, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "exitScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35796, "sourceLowPrice": 1.3547}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30173,13 +30173,13 @@
         </is>
       </c>
       <c r="BJ57" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK57" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782553949007</v>
+        <v>1782575547443</v>
       </c>
       <c r="BM57" t="n">
         <v>1.35578</v>
@@ -30381,12 +30381,12 @@
       </c>
       <c r="DQ57" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR57" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS57" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49533, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "exitScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49533, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "exitScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35988, "sourceLowPrice": 1.35546}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30697,13 +30697,13 @@
         </is>
       </c>
       <c r="BJ58" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK58" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782553949007</v>
+        <v>1782575547444</v>
       </c>
       <c r="BM58" t="n">
         <v>1.35445</v>
@@ -30905,12 +30905,12 @@
       </c>
       <c r="DQ58" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR58" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS58" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49534, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "exitScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49534, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "exitScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37965, "sourceLowPrice": 1.37742}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31221,13 +31221,13 @@
         </is>
       </c>
       <c r="BJ59" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK59" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782553949008</v>
+        <v>1782575547444</v>
       </c>
       <c r="BM59" t="n">
         <v>1.37856</v>
@@ -31429,12 +31429,12 @@
       </c>
       <c r="DQ59" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR59" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS59" t="inlineStr">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49535, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "exitScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49535, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "exitScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38088, "sourceLowPrice": 1.37927}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31745,13 +31745,13 @@
         </is>
       </c>
       <c r="BJ60" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK60" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782553949008</v>
+        <v>1782575547445</v>
       </c>
       <c r="BM60" t="n">
         <v>1.37988</v>
@@ -31953,12 +31953,12 @@
       </c>
       <c r="DQ60" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR60" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS60" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49536, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "exitScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49536, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "exitScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38188, "sourceLowPrice": 1.37862}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32269,13 +32269,13 @@
         </is>
       </c>
       <c r="BJ61" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK61" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782553949008</v>
+        <v>1782575547445</v>
       </c>
       <c r="BM61" t="n">
         <v>1.37802</v>
@@ -32477,12 +32477,12 @@
       </c>
       <c r="DQ61" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR61" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS61" t="inlineStr">
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49537, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "exitScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49537, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "exitScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37672, "sourceLowPrice": 1.3755}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32793,13 +32793,13 @@
         </is>
       </c>
       <c r="BJ62" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK62" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782553949008</v>
+        <v>1782575547445</v>
       </c>
       <c r="BM62" t="n">
         <v>1.37637</v>
@@ -33001,12 +33001,12 @@
       </c>
       <c r="DQ62" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR62" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS62" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49538, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "exitScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49538, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "exitScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37719, "sourceLowPrice": 1.37574}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33317,13 +33317,13 @@
         </is>
       </c>
       <c r="BJ63" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK63" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782553949008</v>
+        <v>1782575547446</v>
       </c>
       <c r="BM63" t="n">
         <v>1.37696</v>
@@ -33525,12 +33525,12 @@
       </c>
       <c r="DQ63" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR63" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS63" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49539, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "exitScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49539, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "exitScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37812, "sourceLowPrice": 1.3746}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33841,13 +33841,13 @@
         </is>
       </c>
       <c r="BJ64" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK64" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782553949009</v>
+        <v>1782575547447</v>
       </c>
       <c r="BM64" t="n">
         <v>1.37743</v>
@@ -34049,12 +34049,12 @@
       </c>
       <c r="DQ64" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR64" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS64" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49540, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "exitScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49540, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "exitScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3767, "sourceLowPrice": 1.37383}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34365,13 +34365,13 @@
         </is>
       </c>
       <c r="BJ65" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK65" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782553949009</v>
+        <v>1782575547447</v>
       </c>
       <c r="BM65" t="n">
         <v>1.37771</v>
@@ -34573,12 +34573,12 @@
       </c>
       <c r="DQ65" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR65" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS65" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49541, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "exitScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49541, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "exitScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37378, "sourceLowPrice": 1.37023}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34889,13 +34889,13 @@
         </is>
       </c>
       <c r="BJ66" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK66" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782553949009</v>
+        <v>1782575547448</v>
       </c>
       <c r="BM66" t="n">
         <v>1.37528</v>
@@ -35097,12 +35097,12 @@
       </c>
       <c r="DQ66" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR66" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS66" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49542, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "exitScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49542, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "exitScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3708, "sourceLowPrice": 1.36661}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35413,13 +35413,13 @@
         </is>
       </c>
       <c r="BJ67" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK67" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782553949010</v>
+        <v>1782575547448</v>
       </c>
       <c r="BM67" t="n">
         <v>1.36636</v>
@@ -35621,12 +35621,12 @@
       </c>
       <c r="DQ67" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR67" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS67" t="inlineStr">
@@ -35888,7 +35888,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49543, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "exitScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49543, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "exitScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36752, "sourceLowPrice": 1.36523}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35937,13 +35937,13 @@
         </is>
       </c>
       <c r="BJ68" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK68" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782553949010</v>
+        <v>1782575547449</v>
       </c>
       <c r="BM68" t="n">
         <v>1.36438</v>
@@ -36145,12 +36145,12 @@
       </c>
       <c r="DQ68" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR68" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS68" t="inlineStr">
@@ -36412,7 +36412,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49544, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "exitScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49544, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "exitScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37707, "sourceLowPrice": 1.37565}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36461,13 +36461,13 @@
         </is>
       </c>
       <c r="BJ69" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK69" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782553949010</v>
+        <v>1782575547449</v>
       </c>
       <c r="BM69" t="n">
         <v>1.37637</v>
@@ -36669,12 +36669,12 @@
       </c>
       <c r="DQ69" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR69" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS69" t="inlineStr">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49545, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49545, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37298, "sourceLowPrice": 1.36951}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36985,13 +36985,13 @@
         </is>
       </c>
       <c r="BJ70" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK70" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782553949010</v>
+        <v>1782575547450</v>
       </c>
       <c r="BM70" t="n">
         <v>1.37313</v>
@@ -37193,12 +37193,12 @@
       </c>
       <c r="DQ70" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR70" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS70" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49546, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "exitScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49546, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "exitScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36662, "sourceLowPrice": 1.36465}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37509,13 +37509,13 @@
         </is>
       </c>
       <c r="BJ71" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK71" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782553949010</v>
+        <v>1782575547451</v>
       </c>
       <c r="BM71" t="n">
         <v>1.36587</v>
@@ -37717,12 +37717,12 @@
       </c>
       <c r="DQ71" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR71" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS71" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49547, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "exitScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49547, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "exitScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36786, "sourceLowPrice": 1.36543}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38033,13 +38033,13 @@
         </is>
       </c>
       <c r="BJ72" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK72" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782553949011</v>
+        <v>1782575547452</v>
       </c>
       <c r="BM72" t="n">
         <v>1.36453</v>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="DQ72" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR72" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS72" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49548, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "exitScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49548, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "exitScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3682, "sourceLowPrice": 1.36696}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38557,13 +38557,13 @@
         </is>
       </c>
       <c r="BJ73" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK73" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782553949011</v>
+        <v>1782575547452</v>
       </c>
       <c r="BM73" t="n">
         <v>1.36747</v>
@@ -38765,12 +38765,12 @@
       </c>
       <c r="DQ73" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR73" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS73" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49549, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "exitScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49549, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "exitScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37174, "sourceLowPrice": 1.36737}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39081,13 +39081,13 @@
         </is>
       </c>
       <c r="BJ74" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK74" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782553949011</v>
+        <v>1782575547452</v>
       </c>
       <c r="BM74" t="n">
         <v>1.36666</v>
@@ -39289,12 +39289,12 @@
       </c>
       <c r="DQ74" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR74" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS74" t="inlineStr">
@@ -39556,7 +39556,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49550, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "exitScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49550, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "exitScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36872, "sourceLowPrice": 1.36762}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39605,13 +39605,13 @@
         </is>
       </c>
       <c r="BJ75" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK75" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782553949011</v>
+        <v>1782575547453</v>
       </c>
       <c r="BM75" t="n">
         <v>1.36781</v>
@@ -39813,12 +39813,12 @@
       </c>
       <c r="DQ75" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR75" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS75" t="inlineStr">
@@ -40080,7 +40080,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49552, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "exitScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49552, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "exitScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36905, "sourceLowPrice": 1.36475}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40129,13 +40129,13 @@
         </is>
       </c>
       <c r="BJ76" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK76" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782553949012</v>
+        <v>1782575547454</v>
       </c>
       <c r="BM76" t="n">
         <v>1.36584</v>
@@ -40337,12 +40337,12 @@
       </c>
       <c r="DQ76" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR76" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS76" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49553, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "exitScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49553, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "exitScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36341, "sourceLowPrice": 1.36098}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40653,13 +40653,13 @@
         </is>
       </c>
       <c r="BJ77" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK77" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782553949012</v>
+        <v>1782575547454</v>
       </c>
       <c r="BM77" t="n">
         <v>1.36438</v>
@@ -40861,12 +40861,12 @@
       </c>
       <c r="DQ77" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR77" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS77" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49554, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "exitScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49554, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "exitScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36221, "sourceLowPrice": 1.36068}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41177,13 +41177,13 @@
         </is>
       </c>
       <c r="BJ78" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK78" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782553949012</v>
+        <v>1782575547454</v>
       </c>
       <c r="BM78" t="n">
         <v>1.36121</v>
@@ -41385,12 +41385,12 @@
       </c>
       <c r="DQ78" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR78" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS78" t="inlineStr">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49555, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "exitScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49555, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "exitScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3627, "sourceLowPrice": 1.35961}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41701,13 +41701,13 @@
         </is>
       </c>
       <c r="BJ79" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK79" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782553949012</v>
+        <v>1782575547455</v>
       </c>
       <c r="BM79" t="n">
         <v>1.36374</v>
@@ -41909,12 +41909,12 @@
       </c>
       <c r="DQ79" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR79" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS79" t="inlineStr">
@@ -42176,7 +42176,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49558, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "exitScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49558, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "exitScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37173, "sourceLowPrice": 1.36522}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42225,13 +42225,13 @@
         </is>
       </c>
       <c r="BJ80" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK80" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782553949012</v>
+        <v>1782575547455</v>
       </c>
       <c r="BM80" t="n">
         <v>1.36464</v>
@@ -42433,12 +42433,12 @@
       </c>
       <c r="DQ80" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR80" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS80" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49560, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "exitScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49560, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "exitScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37134, "sourceLowPrice": 1.36702}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42749,13 +42749,13 @@
         </is>
       </c>
       <c r="BJ81" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK81" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782553949012</v>
+        <v>1782575547456</v>
       </c>
       <c r="BM81" t="n">
         <v>1.37276</v>
@@ -42957,12 +42957,12 @@
       </c>
       <c r="DQ81" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR81" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS81" t="inlineStr">
@@ -43224,7 +43224,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49561, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "exitScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49561, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "exitScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36618, "sourceLowPrice": 1.36321}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43273,13 +43273,13 @@
         </is>
       </c>
       <c r="BJ82" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK82" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782553949013</v>
+        <v>1782575547456</v>
       </c>
       <c r="BM82" t="n">
         <v>1.36667</v>
@@ -43481,12 +43481,12 @@
       </c>
       <c r="DQ82" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR82" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS82" t="inlineStr">
@@ -43748,7 +43748,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49563, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "exitScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49563, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "exitScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36506, "sourceLowPrice": 1.3619}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43797,13 +43797,13 @@
         </is>
       </c>
       <c r="BJ83" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK83" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782553949013</v>
+        <v>1782575547457</v>
       </c>
       <c r="BM83" t="n">
         <v>1.36125</v>
@@ -44005,12 +44005,12 @@
       </c>
       <c r="DQ83" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR83" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS83" t="inlineStr">
@@ -44272,7 +44272,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49475, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "exitScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49475, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "exitScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27972, "sourceLowPrice": 1.2756}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44321,13 +44321,13 @@
         </is>
       </c>
       <c r="BJ84" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK84" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782553949013</v>
+        <v>1782575547457</v>
       </c>
       <c r="BM84" t="n">
         <v>1.27409</v>
@@ -44529,12 +44529,12 @@
       </c>
       <c r="DQ84" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR84" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS84" t="inlineStr">
@@ -44796,7 +44796,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49476, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "exitScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49476, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "exitScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27954, "sourceLowPrice": 1.27836}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44845,13 +44845,13 @@
         </is>
       </c>
       <c r="BJ85" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK85" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782553949013</v>
+        <v>1782575547458</v>
       </c>
       <c r="BM85" t="n">
         <v>1.27921</v>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="DQ85" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR85" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS85" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49478, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "exitScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49478, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "exitScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2778, "sourceLowPrice": 1.27624}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45369,13 +45369,13 @@
         </is>
       </c>
       <c r="BJ86" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK86" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782553949013</v>
+        <v>1782575547458</v>
       </c>
       <c r="BM86" t="n">
         <v>1.2764</v>
@@ -45577,12 +45577,12 @@
       </c>
       <c r="DQ86" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR86" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS86" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49479, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49479, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28174, "sourceLowPrice": 1.27684}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45893,13 +45893,13 @@
         </is>
       </c>
       <c r="BJ87" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK87" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782553949014</v>
+        <v>1782575547459</v>
       </c>
       <c r="BM87" t="n">
         <v>1.27601</v>
@@ -46101,12 +46101,12 @@
       </c>
       <c r="DQ87" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR87" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS87" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49480, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "exitScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49480, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "exitScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27496, "sourceLowPrice": 1.27134}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46417,13 +46417,13 @@
         </is>
       </c>
       <c r="BJ88" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK88" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782553949014</v>
+        <v>1782575547460</v>
       </c>
       <c r="BM88" t="n">
         <v>1.27029</v>
@@ -46625,12 +46625,12 @@
       </c>
       <c r="DQ88" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR88" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS88" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49481, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "exitScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49481, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "exitScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26807, "sourceLowPrice": 1.2669}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46941,13 +46941,13 @@
         </is>
       </c>
       <c r="BJ89" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK89" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782553949014</v>
+        <v>1782575547460</v>
       </c>
       <c r="BM89" t="n">
         <v>1.26765</v>
@@ -47149,12 +47149,12 @@
       </c>
       <c r="DQ89" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR89" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS89" t="inlineStr">
@@ -47416,7 +47416,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49482, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "exitScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49482, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "exitScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27294, "sourceLowPrice": 1.26772}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47465,13 +47465,13 @@
         </is>
       </c>
       <c r="BJ90" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK90" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782553949015</v>
+        <v>1782575547461</v>
       </c>
       <c r="BM90" t="n">
         <v>1.27424</v>
@@ -47673,12 +47673,12 @@
       </c>
       <c r="DQ90" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR90" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS90" t="inlineStr">
@@ -47940,7 +47940,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49564, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "exitScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49564, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "exitScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27342, "sourceLowPrice": 1.26874}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47989,13 +47989,13 @@
         </is>
       </c>
       <c r="BJ91" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK91" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782553949015</v>
+        <v>1782575547462</v>
       </c>
       <c r="BM91" t="n">
         <v>1.27425</v>
@@ -48197,12 +48197,12 @@
       </c>
       <c r="DQ91" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR91" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS91" t="inlineStr">
@@ -48464,7 +48464,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49565, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "exitScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49565, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "exitScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26962, "sourceLowPrice": 1.26396}</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -48513,13 +48513,13 @@
         </is>
       </c>
       <c r="BJ92" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK92" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL92" t="n">
-        <v>1782553949016</v>
+        <v>1782575547463</v>
       </c>
       <c r="BM92" t="n">
         <v>1.26985</v>
@@ -48721,12 +48721,12 @@
       </c>
       <c r="DQ92" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR92" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS92" t="inlineStr">
@@ -48988,7 +48988,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49566, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "exitScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49566, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "exitScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26542, "sourceLowPrice": 1.26182}</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -49037,13 +49037,13 @@
         </is>
       </c>
       <c r="BJ93" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK93" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL93" t="n">
-        <v>1782553949016</v>
+        <v>1782575547464</v>
       </c>
       <c r="BM93" t="n">
         <v>1.26656</v>
@@ -49245,12 +49245,12 @@
       </c>
       <c r="DQ93" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR93" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS93" t="inlineStr">
@@ -49512,7 +49512,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49567, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "exitScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49567, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "exitScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26708, "sourceLowPrice": 1.26466}</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -49561,13 +49561,13 @@
         </is>
       </c>
       <c r="BJ94" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK94" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL94" t="n">
-        <v>1782553949016</v>
+        <v>1782575547464</v>
       </c>
       <c r="BM94" t="n">
         <v>1.26364</v>
@@ -49769,12 +49769,12 @@
       </c>
       <c r="DQ94" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR94" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS94" t="inlineStr">
@@ -50036,7 +50036,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49568, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "exitScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49568, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "exitScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2666, "sourceLowPrice": 1.26465}</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -50085,13 +50085,13 @@
         </is>
       </c>
       <c r="BJ95" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK95" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL95" t="n">
-        <v>1782553949016</v>
+        <v>1782575547464</v>
       </c>
       <c r="BM95" t="n">
         <v>1.26609</v>
@@ -50293,12 +50293,12 @@
       </c>
       <c r="DQ95" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR95" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS95" t="inlineStr">
@@ -50560,7 +50560,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49569, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49569, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26553, "sourceLowPrice": 1.26198}</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -50609,13 +50609,13 @@
         </is>
       </c>
       <c r="BJ96" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK96" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL96" t="n">
-        <v>1782553949016</v>
+        <v>1782575547465</v>
       </c>
       <c r="BM96" t="n">
         <v>1.26671</v>
@@ -50817,12 +50817,12 @@
       </c>
       <c r="DQ96" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR96" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS96" t="inlineStr">
@@ -51084,7 +51084,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49570, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "exitScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49570, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "exitScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.269, "sourceLowPrice": 1.26706}</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -51133,13 +51133,13 @@
         </is>
       </c>
       <c r="BJ97" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK97" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL97" t="n">
-        <v>1782553949017</v>
+        <v>1782575547465</v>
       </c>
       <c r="BM97" t="n">
         <v>1.2683</v>
@@ -51341,12 +51341,12 @@
       </c>
       <c r="DQ97" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR97" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS97" t="inlineStr">
@@ -51608,7 +51608,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49571, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "exitScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49571, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "exitScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26739, "sourceLowPrice": 1.26578}</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -51657,13 +51657,13 @@
         </is>
       </c>
       <c r="BJ98" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK98" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL98" t="n">
-        <v>1782553949017</v>
+        <v>1782575547466</v>
       </c>
       <c r="BM98" t="n">
         <v>1.26653</v>
@@ -51865,12 +51865,12 @@
       </c>
       <c r="DQ98" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR98" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS98" t="inlineStr">
@@ -52132,7 +52132,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49572, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49572, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26895, "sourceLowPrice": 1.267}</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -52181,13 +52181,13 @@
         </is>
       </c>
       <c r="BJ99" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK99" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL99" t="n">
-        <v>1782553949017</v>
+        <v>1782575547467</v>
       </c>
       <c r="BM99" t="n">
         <v>1.26866</v>
@@ -52389,12 +52389,12 @@
       </c>
       <c r="DQ99" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR99" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS99" t="inlineStr">
@@ -52656,7 +52656,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49573, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "exitScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49573, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "exitScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27677, "sourceLowPrice": 1.27504}</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -52705,13 +52705,13 @@
         </is>
       </c>
       <c r="BJ100" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK100" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL100" t="n">
-        <v>1782553949018</v>
+        <v>1782575547468</v>
       </c>
       <c r="BM100" t="n">
         <v>1.27449</v>
@@ -52913,12 +52913,12 @@
       </c>
       <c r="DQ100" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR100" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS100" t="inlineStr">
@@ -53180,7 +53180,7 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49574, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "exitScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49574, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "exitScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28217, "sourceLowPrice": 1.27805}</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
@@ -53229,13 +53229,13 @@
         </is>
       </c>
       <c r="BJ101" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BK101" t="n">
-        <v>947289</v>
+        <v>32</v>
       </c>
       <c r="BL101" t="n">
-        <v>1782553949018</v>
+        <v>1782575547468</v>
       </c>
       <c r="BM101" t="n">
         <v>1.28269</v>
@@ -53437,12 +53437,12 @@
       </c>
       <c r="DQ101" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DR101" t="inlineStr">
         <is>
-          <t>journalAccount:947289</t>
+          <t>journalAccount:54</t>
         </is>
       </c>
       <c r="DS101" t="inlineStr">

--- a/mentor data/haider 8-talaria-adapted.xlsx
+++ b/mentor data/haider 8-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49407, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "exitScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33718, "sourceLowPrice": 1.33432}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49407, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "exitScreenshotUrl": "https://www.tradingview.com/x/kQfROZOg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33718, "sourceLowPrice": 1.33432, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782575547415</v>
+        <v>1782578952925</v>
       </c>
       <c r="BM2" t="n">
         <v>1.33374</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.33374, "new": 1.33344, "at": 1704277500000}]</t>
         </is>
       </c>
       <c r="DP2" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49408, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "exitScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33661, "sourceLowPrice": 1.33377}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49408, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "exitScreenshotUrl": "https://www.tradingview.com/x/PdBX6ApN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33661, "sourceLowPrice": 1.33377, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>32</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782575547416</v>
+        <v>1782578952926</v>
       </c>
       <c r="BM3" t="n">
         <v>1.33277</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49409, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "exitScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33868, "sourceLowPrice": 1.33594}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49409, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "exitScreenshotUrl": "https://www.tradingview.com/x/nRsYkr20/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33868, "sourceLowPrice": 1.33594, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2407,7 +2407,7 @@
         <v>32</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782575547417</v>
+        <v>1782578952926</v>
       </c>
       <c r="BM4" t="n">
         <v>1.33741</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49411, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "exitScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34019, "sourceLowPrice": 1.33606}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49411, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "exitScreenshotUrl": "https://www.tradingview.com/x/j8qvkXLR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34019, "sourceLowPrice": 1.33606, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2931,7 +2931,7 @@
         <v>32</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782575547417</v>
+        <v>1782578952926</v>
       </c>
       <c r="BM5" t="n">
         <v>1.33501</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49413, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "exitScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33908, "sourceLowPrice": 1.3357}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49413, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "exitScreenshotUrl": "https://www.tradingview.com/x/8DdlH8CL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33908, "sourceLowPrice": 1.3357, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3455,7 +3455,7 @@
         <v>32</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782575547418</v>
+        <v>1782578952927</v>
       </c>
       <c r="BM6" t="n">
         <v>1.33924</v>
@@ -3636,11 +3636,11 @@
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "late_entry", "label": "Late Entry", "source": "manual", "state": "confirmed", "cost_R": 2.26, "cost_$": 2260, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-01-10T18:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49414, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "exitScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33714, "sourceLowPrice": 1.33506}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49414, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "exitScreenshotUrl": "https://www.tradingview.com/x/reoRW0pc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33714, "sourceLowPrice": 1.33506, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>32</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782575547418</v>
+        <v>1782578952927</v>
       </c>
       <c r="BM7" t="n">
         <v>1.338</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49415, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "exitScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33866, "sourceLowPrice": 1.33434}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49415, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "exitScreenshotUrl": "https://www.tradingview.com/x/evQ45x4G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.33866, "sourceLowPrice": 1.33434, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4503,7 +4503,7 @@
         <v>32</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782575547419</v>
+        <v>1782578952928</v>
       </c>
       <c r="BM8" t="n">
         <v>1.33873</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.33873, "new": 1.33896, "at": 1705044000000}]</t>
         </is>
       </c>
       <c r="DP8" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49416, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "exitScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34403, "sourceLowPrice": 1.3413}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49416, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "exitScreenshotUrl": "https://www.tradingview.com/x/VDb9wgxo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34403, "sourceLowPrice": 1.3413, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5027,7 +5027,7 @@
         <v>32</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782575547419</v>
+        <v>1782578952928</v>
       </c>
       <c r="BM9" t="n">
         <v>1.3408</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49417, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "exitScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34777, "sourceLowPrice": 1.34452}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49417, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "exitScreenshotUrl": "https://www.tradingview.com/x/meBUk3Bd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34777, "sourceLowPrice": 1.34452, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5551,7 +5551,7 @@
         <v>32</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782575547419</v>
+        <v>1782578952928</v>
       </c>
       <c r="BM10" t="n">
         <v>1.34696</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49418, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "exitScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35019, "sourceLowPrice": 1.3457}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49418, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "exitScreenshotUrl": "https://www.tradingview.com/x/4eVRVFur/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35019, "sourceLowPrice": 1.3457, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6075,7 +6075,7 @@
         <v>32</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782575547420</v>
+        <v>1782578952929</v>
       </c>
       <c r="BM11" t="n">
         <v>1.34425</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49419, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "exitScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35358, "sourceLowPrice": 1.35056}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49419, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "exitScreenshotUrl": "https://www.tradingview.com/x/eQfoLuiN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35358, "sourceLowPrice": 1.35056, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6599,7 +6599,7 @@
         <v>32</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782575547420</v>
+        <v>1782578952929</v>
       </c>
       <c r="BM12" t="n">
         <v>1.35019</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49420, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35272, "sourceLowPrice": 1.34827}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49420, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/ZjfrkGMK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35272, "sourceLowPrice": 1.34827, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7123,7 +7123,7 @@
         <v>32</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782575547421</v>
+        <v>1782578952929</v>
       </c>
       <c r="BM13" t="n">
         <v>1.34802</v>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49421, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "exitScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34868, "sourceLowPrice": 1.34402}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49421, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "exitScreenshotUrl": "https://www.tradingview.com/x/68p7iTGw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34868, "sourceLowPrice": 1.34402, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7647,7 +7647,7 @@
         <v>32</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782575547422</v>
+        <v>1782578952930</v>
       </c>
       <c r="BM14" t="n">
         <v>1.34969</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49422, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34586, "sourceLowPrice": 1.3426}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49422, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/eBjha5NJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34586, "sourceLowPrice": 1.3426, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>32</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782575547422</v>
+        <v>1782578952930</v>
       </c>
       <c r="BM15" t="n">
         <v>1.34502</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49468, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "exitScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3492, "sourceLowPrice": 1.3467}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49468, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "exitScreenshotUrl": "https://www.tradingview.com/x/Ycg6PYle/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3492, "sourceLowPrice": 1.3467, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8695,7 +8695,7 @@
         <v>32</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782575547423</v>
+        <v>1782578952930</v>
       </c>
       <c r="BM16" t="n">
         <v>1.34627</v>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
         <v>2.67</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49469, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35162, "sourceLowPrice": 1.34733}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49469, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/abGSmjG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35162, "sourceLowPrice": 1.34733, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9219,7 +9219,7 @@
         <v>32</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782575547423</v>
+        <v>1782578952930</v>
       </c>
       <c r="BM17" t="n">
         <v>1.34689</v>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49470, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "exitScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35192, "sourceLowPrice": 1.34855}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49470, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "exitScreenshotUrl": "https://www.tradingview.com/x/XbE9DQcE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35192, "sourceLowPrice": 1.34855, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9743,7 +9743,7 @@
         <v>32</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782575547424</v>
+        <v>1782578952931</v>
       </c>
       <c r="BM18" t="n">
         <v>1.34981</v>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49471, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "exitScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34547, "sourceLowPrice": 1.34352}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49471, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "exitScreenshotUrl": "https://www.tradingview.com/x/EiLbBhLB/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34547, "sourceLowPrice": 1.34352, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>32</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782575547425</v>
+        <v>1782578952931</v>
       </c>
       <c r="BM19" t="n">
         <v>1.34446</v>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49472, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "exitScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34466, "sourceLowPrice": 1.34302}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49472, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "exitScreenshotUrl": "https://www.tradingview.com/x/qsPIKoYe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34466, "sourceLowPrice": 1.34302, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>32</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782575547425</v>
+        <v>1782578952931</v>
       </c>
       <c r="BM20" t="n">
         <v>1.3441</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49473, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "exitScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34372, "sourceLowPrice": 1.34008}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49473, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "exitScreenshotUrl": "https://www.tradingview.com/x/ojvGY6qa/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34372, "sourceLowPrice": 1.34008, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11315,7 +11315,7 @@
         <v>32</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782575547425</v>
+        <v>1782578952931</v>
       </c>
       <c r="BM21" t="n">
         <v>1.34492</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49474, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34478, "sourceLowPrice": 1.34124}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49474, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "exitScreenshotUrl": "https://www.tradingview.com/x/8S5pOvG5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34478, "sourceLowPrice": 1.34124, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11839,7 +11839,7 @@
         <v>32</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782575547426</v>
+        <v>1782578952932</v>
       </c>
       <c r="BM22" t="n">
         <v>1.34562</v>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49477, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "exitScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27952, "sourceLowPrice": 1.27554}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49477, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "exitScreenshotUrl": "https://www.tradingview.com/x/XGDCV733/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27952, "sourceLowPrice": 1.27554, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>32</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782575547426</v>
+        <v>1782578952932</v>
       </c>
       <c r="BM23" t="n">
         <v>1.2798</v>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49490, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "exitScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35433, "sourceLowPrice": 1.35118}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49490, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "exitScreenshotUrl": "https://www.tradingview.com/x/KQQNJPrT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35433, "sourceLowPrice": 1.35118, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12887,7 +12887,7 @@
         <v>32</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782575547426</v>
+        <v>1782578952932</v>
       </c>
       <c r="BM24" t="n">
         <v>1.35455</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49491, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "exitScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34807, "sourceLowPrice": 1.3455}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49491, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "exitScreenshotUrl": "https://www.tradingview.com/x/louGKOqK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34807, "sourceLowPrice": 1.3455, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13411,7 +13411,7 @@
         <v>32</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782575547427</v>
+        <v>1782578952932</v>
       </c>
       <c r="BM25" t="n">
         <v>1.34881</v>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="BO25" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="BP25" t="n">
         <v>2</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49492, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "exitScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3469, "sourceLowPrice": 1.34524}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49492, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "exitScreenshotUrl": "https://www.tradingview.com/x/8kE0zMi0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3469, "sourceLowPrice": 1.34524, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13935,7 +13935,7 @@
         <v>32</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782575547427</v>
+        <v>1782578952932</v>
       </c>
       <c r="BM26" t="n">
         <v>1.34575</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49493, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "exitScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34818, "sourceLowPrice": 1.34311}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49493, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "exitScreenshotUrl": "https://www.tradingview.com/x/eY7dsMH2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34818, "sourceLowPrice": 1.34311, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14459,7 +14459,7 @@
         <v>32</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782575547428</v>
+        <v>1782578952933</v>
       </c>
       <c r="BM27" t="n">
         <v>1.34289</v>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49494, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "exitScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35076, "sourceLowPrice": 1.34759}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49494, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "exitScreenshotUrl": "https://www.tradingview.com/x/zEdW7zfC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35076, "sourceLowPrice": 1.34759, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14983,7 +14983,7 @@
         <v>32</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782575547428</v>
+        <v>1782578952933</v>
       </c>
       <c r="BM28" t="n">
         <v>1.34694</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49495, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "exitScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3526, "sourceLowPrice": 1.35139}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49495, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "exitScreenshotUrl": "https://www.tradingview.com/x/eg0xFWU1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3526, "sourceLowPrice": 1.35139, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15507,7 +15507,7 @@
         <v>32</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782575547429</v>
+        <v>1782578952933</v>
       </c>
       <c r="BM29" t="n">
         <v>1.35174</v>
@@ -15688,11 +15688,11 @@
       </c>
       <c r="DL29" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN29" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="EF29" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49496, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "exitScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35236, "sourceLowPrice": 1.35056}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49496, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "exitScreenshotUrl": "https://www.tradingview.com/x/EzYs95cK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35236, "sourceLowPrice": 1.35056, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16031,7 +16031,7 @@
         <v>32</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782575547429</v>
+        <v>1782578952933</v>
       </c>
       <c r="BM30" t="n">
         <v>1.35116</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49497, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "exitScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35, "sourceLowPrice": 1.34682}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49497, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "exitScreenshotUrl": "https://www.tradingview.com/x/10QcAQaU/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35, "sourceLowPrice": 1.34682, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16555,7 +16555,7 @@
         <v>32</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782575547430</v>
+        <v>1782578952934</v>
       </c>
       <c r="BM31" t="n">
         <v>1.34593</v>
@@ -16736,11 +16736,11 @@
       </c>
       <c r="DL31" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN31" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="EF31" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49498, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "exitScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35191, "sourceLowPrice": 1.35014}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49498, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "exitScreenshotUrl": "https://www.tradingview.com/x/noZCeofx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35191, "sourceLowPrice": 1.35014, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17079,7 +17079,7 @@
         <v>32</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782575547430</v>
+        <v>1782578952934</v>
       </c>
       <c r="BM32" t="n">
         <v>1.35106</v>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49499, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "exitScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35331, "sourceLowPrice": 1.34914}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49499, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "exitScreenshotUrl": "https://www.tradingview.com/x/q8Igii9L/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35331, "sourceLowPrice": 1.34914, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17603,7 +17603,7 @@
         <v>32</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782575547431</v>
+        <v>1782578952934</v>
       </c>
       <c r="BM33" t="n">
         <v>1.34827</v>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49508, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "exitScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35638, "sourceLowPrice": 1.35411}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49508, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "exitScreenshotUrl": "https://www.tradingview.com/x/7btugIFr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35638, "sourceLowPrice": 1.35411, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18127,7 +18127,7 @@
         <v>32</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782575547431</v>
+        <v>1782578952934</v>
       </c>
       <c r="BM34" t="n">
         <v>1.35505</v>
@@ -18308,11 +18308,11 @@
       </c>
       <c r="DL34" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN34" t="inlineStr">
         <is>
@@ -18386,12 +18386,12 @@
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-02-29T10:00:00.000Z"}, {"type": "late_entry", "label": "Late Entry", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-02-29T10:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49509, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "exitScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35852, "sourceLowPrice": 1.35502}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49509, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "exitScreenshotUrl": "https://www.tradingview.com/x/Q3xhTs5F/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35852, "sourceLowPrice": 1.35502, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18651,7 +18651,7 @@
         <v>32</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782575547431</v>
+        <v>1782578952935</v>
       </c>
       <c r="BM35" t="n">
         <v>1.35387</v>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49510, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "exitScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36018, "sourceLowPrice": 1.35717}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49510, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "exitScreenshotUrl": "https://www.tradingview.com/x/qTLVAufP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36018, "sourceLowPrice": 1.35717, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19175,7 +19175,7 @@
         <v>32</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782575547432</v>
+        <v>1782578952935</v>
       </c>
       <c r="BM36" t="n">
         <v>1.3567</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="DO36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.3567, "new": 1.35656, "at": 1709278140000}]</t>
         </is>
       </c>
       <c r="DP36" t="n">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49511, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "exitScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35837, "sourceLowPrice": 1.35614}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49511, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "exitScreenshotUrl": "https://www.tradingview.com/x/G4exPkz4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35837, "sourceLowPrice": 1.35614, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19699,7 +19699,7 @@
         <v>32</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782575547432</v>
+        <v>1782578952935</v>
       </c>
       <c r="BM37" t="n">
         <v>1.35561</v>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49512, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "exitScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35854, "sourceLowPrice": 1.35732}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49512, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "exitScreenshotUrl": "https://www.tradingview.com/x/BXA3zXtG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35854, "sourceLowPrice": 1.35732, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20223,7 +20223,7 @@
         <v>32</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782575547432</v>
+        <v>1782578952935</v>
       </c>
       <c r="BM38" t="n">
         <v>1.35772</v>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49513, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "exitScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35784, "sourceLowPrice": 1.35561}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49513, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "exitScreenshotUrl": "https://www.tradingview.com/x/Wahktekx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35784, "sourceLowPrice": 1.35561, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20747,7 +20747,7 @@
         <v>32</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782575547433</v>
+        <v>1782578952935</v>
       </c>
       <c r="BM39" t="n">
         <v>1.35684</v>
@@ -20928,11 +20928,11 @@
       </c>
       <c r="DL39" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN39" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49514, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "exitScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34914, "sourceLowPrice": 1.34712}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49514, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "exitScreenshotUrl": "https://www.tradingview.com/x/DiqojhQF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34914, "sourceLowPrice": 1.34712, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v>32</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782575547433</v>
+        <v>1782578952936</v>
       </c>
       <c r="BM40" t="n">
         <v>1.34799</v>
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49515, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "exitScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34944, "sourceLowPrice": 1.34661}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49515, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "exitScreenshotUrl": "https://www.tradingview.com/x/U5ePprdy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.34944, "sourceLowPrice": 1.34661, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21795,7 +21795,7 @@
         <v>32</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782575547434</v>
+        <v>1782578952936</v>
       </c>
       <c r="BM41" t="n">
         <v>1.34999</v>
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49517, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35514, "sourceLowPrice": 1.35128}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49517, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkQ8qsVW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35514, "sourceLowPrice": 1.35128, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22319,7 +22319,7 @@
         <v>32</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782575547434</v>
+        <v>1782578952936</v>
       </c>
       <c r="BM42" t="n">
         <v>1.35072</v>
@@ -22500,11 +22500,11 @@
       </c>
       <c r="DL42" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN42" t="inlineStr">
         <is>
@@ -22578,12 +22578,12 @@
       </c>
       <c r="EF42" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 2000, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-03-15T12:19:00.000Z"}, {"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 2000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-03-15T12:19:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH42" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49518, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "exitScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35518, "sourceLowPrice": 1.3531}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49518, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "exitScreenshotUrl": "https://www.tradingview.com/x/S9UKhNNb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35518, "sourceLowPrice": 1.3531, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22843,7 +22843,7 @@
         <v>32</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782575547435</v>
+        <v>1782578952936</v>
       </c>
       <c r="BM43" t="n">
         <v>1.35485</v>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49519, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "exitScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35912, "sourceLowPrice": 1.35754}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49519, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "exitScreenshotUrl": "https://www.tradingview.com/x/RbJntGJW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35912, "sourceLowPrice": 1.35754, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23367,7 +23367,7 @@
         <v>32</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782575547435</v>
+        <v>1782578952937</v>
       </c>
       <c r="BM44" t="n">
         <v>1.35812</v>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="DO44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.35812, "new": 1.35795, "at": 1710925800000}]</t>
         </is>
       </c>
       <c r="DP44" t="n">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49520, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "exitScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35419, "sourceLowPrice": 1.35054}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49520, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "exitScreenshotUrl": "https://www.tradingview.com/x/yC5r0q2B/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35419, "sourceLowPrice": 1.35054, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23891,7 +23891,7 @@
         <v>32</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782575547436</v>
+        <v>1782578952937</v>
       </c>
       <c r="BM45" t="n">
         <v>1.34948</v>
@@ -24072,11 +24072,11 @@
       </c>
       <c r="DL45" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN45" t="inlineStr">
         <is>
@@ -24150,12 +24150,12 @@
       </c>
       <c r="EF45" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 2000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-03-21T11:43:00.000Z"}, {"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 2000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-03-21T11:43:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH45" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49521, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49521, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24415,7 +24415,7 @@
         <v>32</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782575547437</v>
+        <v>1782578952937</v>
       </c>
       <c r="BM46" t="n">
         <v>1.356</v>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49522, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49522, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "exitScreenshotUrl": "https://www.tradingview.com/x/U97D0sAv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36053, "sourceLowPrice": 1.3564, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24939,7 +24939,7 @@
         <v>32</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782575547436</v>
+        <v>1782578952937</v>
       </c>
       <c r="BM47" t="n">
         <v>1.356</v>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49523, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35762}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49523, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8BqHexz2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35762, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25463,7 +25463,7 @@
         <v>32</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782575547437</v>
+        <v>1782578952937</v>
       </c>
       <c r="BM48" t="n">
         <v>1.35851</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49524, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "exitScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35822, "sourceLowPrice": 1.35611}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49524, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "exitScreenshotUrl": "https://www.tradingview.com/x/4hMngGsk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35822, "sourceLowPrice": 1.35611, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25987,7 +25987,7 @@
         <v>32</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782575547438</v>
+        <v>1782578952938</v>
       </c>
       <c r="BM49" t="n">
         <v>1.35678</v>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49525, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "exitScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35856, "sourceLowPrice": 1.35682}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49525, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "exitScreenshotUrl": "https://www.tradingview.com/x/c19Rfpjn/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35856, "sourceLowPrice": 1.35682, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26511,7 +26511,7 @@
         <v>32</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782575547439</v>
+        <v>1782578952938</v>
       </c>
       <c r="BM50" t="n">
         <v>1.35798</v>
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49526, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "exitScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3595, "sourceLowPrice": 1.35769}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49526, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "exitScreenshotUrl": "https://www.tradingview.com/x/vfFcaYHg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3595, "sourceLowPrice": 1.35769, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27035,7 +27035,7 @@
         <v>32</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782575547439</v>
+        <v>1782578952939</v>
       </c>
       <c r="BM51" t="n">
         <v>1.35865</v>
@@ -27216,11 +27216,11 @@
       </c>
       <c r="DL51" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN51" t="inlineStr">
         <is>
@@ -27294,12 +27294,12 @@
       </c>
       <c r="EF51" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2025-03-27T10:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH51" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49527, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "exitScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35849, "sourceLowPrice": 1.35558}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49527, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "exitScreenshotUrl": "https://www.tradingview.com/x/synQNIwd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35849, "sourceLowPrice": 1.35558, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27559,7 +27559,7 @@
         <v>32</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782575547440</v>
+        <v>1782578952939</v>
       </c>
       <c r="BM52" t="n">
         <v>1.35425</v>
@@ -27740,11 +27740,11 @@
       </c>
       <c r="DL52" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN52" t="inlineStr">
         <is>
@@ -27818,12 +27818,12 @@
       </c>
       <c r="EF52" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "early_exit", "label": "Early Exit", "source": "manual", "state": "confirmed", "cost_R": 2.0, "cost_$": 2000, "evidence": "Closed before the planned target without a rule-based trigger.", "detected_at": "2024-04-01T11:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH52" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49528, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35696, "sourceLowPrice": 1.35494}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49528, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Q2QwKOD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35696, "sourceLowPrice": 1.35494, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28083,7 +28083,7 @@
         <v>32</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782575547440</v>
+        <v>1782578952939</v>
       </c>
       <c r="BM53" t="n">
         <v>1.35603</v>
@@ -28264,11 +28264,11 @@
       </c>
       <c r="DL53" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN53" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49529, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "exitScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36086, "sourceLowPrice": 1.35546}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49529, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "exitScreenshotUrl": "https://www.tradingview.com/x/nK2dWF2H/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36086, "sourceLowPrice": 1.35546, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28607,7 +28607,7 @@
         <v>32</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782575547440</v>
+        <v>1782578952939</v>
       </c>
       <c r="BM54" t="n">
         <v>1.35476</v>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49530, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "exitScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35694}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49530, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "exitScreenshotUrl": "https://www.tradingview.com/x/RUWAhoT7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35926, "sourceLowPrice": 1.35694, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29131,7 +29131,7 @@
         <v>32</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782575547441</v>
+        <v>1782578952940</v>
       </c>
       <c r="BM55" t="n">
         <v>1.35841</v>
@@ -29600,7 +29600,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49531, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35999, "sourceLowPrice": 1.3577}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49531, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7CrSrmc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35999, "sourceLowPrice": 1.3577, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29655,7 +29655,7 @@
         <v>32</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782575547441</v>
+        <v>1782578952940</v>
       </c>
       <c r="BM56" t="n">
         <v>1.3567</v>
@@ -30124,7 +30124,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49532, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "exitScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35796, "sourceLowPrice": 1.3547}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49532, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "exitScreenshotUrl": "https://www.tradingview.com/x/fzQoMmf2/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35796, "sourceLowPrice": 1.3547, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30179,7 +30179,7 @@
         <v>32</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782575547443</v>
+        <v>1782578952940</v>
       </c>
       <c r="BM57" t="n">
         <v>1.35578</v>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49533, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "exitScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35988, "sourceLowPrice": 1.35546}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49533, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "exitScreenshotUrl": "https://www.tradingview.com/x/VAU5SjkR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.35988, "sourceLowPrice": 1.35546, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30703,7 +30703,7 @@
         <v>32</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782575547444</v>
+        <v>1782578952941</v>
       </c>
       <c r="BM58" t="n">
         <v>1.35445</v>
@@ -31172,7 +31172,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49534, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "exitScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37965, "sourceLowPrice": 1.37742}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49534, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "exitScreenshotUrl": "https://www.tradingview.com/x/sN3afiZv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37965, "sourceLowPrice": 1.37742, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31227,7 +31227,7 @@
         <v>32</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782575547444</v>
+        <v>1782578952941</v>
       </c>
       <c r="BM59" t="n">
         <v>1.37856</v>
@@ -31696,7 +31696,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49535, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "exitScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38088, "sourceLowPrice": 1.37927}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49535, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "exitScreenshotUrl": "https://www.tradingview.com/x/9elj3zxR/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38088, "sourceLowPrice": 1.37927, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31751,7 +31751,7 @@
         <v>32</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782575547445</v>
+        <v>1782578952941</v>
       </c>
       <c r="BM60" t="n">
         <v>1.37988</v>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49536, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "exitScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38188, "sourceLowPrice": 1.37862}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49536, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "exitScreenshotUrl": "https://www.tradingview.com/x/skWTQ9nS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.38188, "sourceLowPrice": 1.37862, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32275,7 +32275,7 @@
         <v>32</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782575547445</v>
+        <v>1782578952941</v>
       </c>
       <c r="BM61" t="n">
         <v>1.37802</v>
@@ -32456,11 +32456,11 @@
       </c>
       <c r="DL61" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN61" t="inlineStr">
         <is>
@@ -32534,12 +32534,12 @@
       </c>
       <c r="EF61" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 2000, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-04-17T12:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH61" t="inlineStr">
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49537, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "exitScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37672, "sourceLowPrice": 1.3755}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49537, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "exitScreenshotUrl": "https://www.tradingview.com/x/I5h8rZ42/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37672, "sourceLowPrice": 1.3755, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32799,7 +32799,7 @@
         <v>32</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782575547445</v>
+        <v>1782578952942</v>
       </c>
       <c r="BM62" t="n">
         <v>1.37637</v>
@@ -32980,11 +32980,11 @@
       </c>
       <c r="DL62" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN62" t="inlineStr">
         <is>
@@ -33058,12 +33058,12 @@
       </c>
       <c r="EF62" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-04-18T08:28:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH62" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49538, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "exitScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37719, "sourceLowPrice": 1.37574}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49538, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "exitScreenshotUrl": "https://www.tradingview.com/x/ei04GmQe/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37719, "sourceLowPrice": 1.37574, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33323,7 +33323,7 @@
         <v>32</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782575547446</v>
+        <v>1782578952942</v>
       </c>
       <c r="BM63" t="n">
         <v>1.37696</v>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49539, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "exitScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37812, "sourceLowPrice": 1.3746}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49539, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "exitScreenshotUrl": "https://www.tradingview.com/x/wwPo1LfL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37812, "sourceLowPrice": 1.3746, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33847,7 +33847,7 @@
         <v>32</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782575547447</v>
+        <v>1782578952943</v>
       </c>
       <c r="BM64" t="n">
         <v>1.37743</v>
@@ -34028,11 +34028,11 @@
       </c>
       <c r="DL64" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN64" t="inlineStr">
         <is>
@@ -34106,12 +34106,12 @@
       </c>
       <c r="EF64" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2024-04-18T18:00:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH64" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49540, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "exitScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3767, "sourceLowPrice": 1.37383}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49540, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "exitScreenshotUrl": "https://www.tradingview.com/x/21yPtz5S/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3767, "sourceLowPrice": 1.37383, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34371,7 +34371,7 @@
         <v>32</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782575547447</v>
+        <v>1782578952943</v>
       </c>
       <c r="BM65" t="n">
         <v>1.37771</v>
@@ -34840,7 +34840,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49541, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "exitScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37378, "sourceLowPrice": 1.37023}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49541, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "exitScreenshotUrl": "https://www.tradingview.com/x/5tqjCaAc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37378, "sourceLowPrice": 1.37023, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34895,7 +34895,7 @@
         <v>32</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782575547448</v>
+        <v>1782578952943</v>
       </c>
       <c r="BM66" t="n">
         <v>1.37528</v>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49542, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "exitScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3708, "sourceLowPrice": 1.36661}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49542, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "exitScreenshotUrl": "https://www.tradingview.com/x/MhmWVeBL/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3708, "sourceLowPrice": 1.36661, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35419,7 +35419,7 @@
         <v>32</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782575547448</v>
+        <v>1782578952943</v>
       </c>
       <c r="BM67" t="n">
         <v>1.36636</v>
@@ -35888,7 +35888,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49543, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "exitScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36752, "sourceLowPrice": 1.36523}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49543, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "exitScreenshotUrl": "https://www.tradingview.com/x/EDeY9rbC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36752, "sourceLowPrice": 1.36523, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35943,7 +35943,7 @@
         <v>32</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782575547449</v>
+        <v>1782578952944</v>
       </c>
       <c r="BM68" t="n">
         <v>1.36438</v>
@@ -36412,7 +36412,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49544, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "exitScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37707, "sourceLowPrice": 1.37565}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49544, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "exitScreenshotUrl": "https://www.tradingview.com/x/jaAoBNyi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37707, "sourceLowPrice": 1.37565, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36467,7 +36467,7 @@
         <v>32</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782575547449</v>
+        <v>1782578952944</v>
       </c>
       <c r="BM69" t="n">
         <v>1.37637</v>
@@ -36648,11 +36648,11 @@
       </c>
       <c r="DL69" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN69" t="inlineStr">
         <is>
@@ -36726,12 +36726,12 @@
       </c>
       <c r="EF69" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "late_entry", "label": "Late Entry", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-05-01T08:45:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49545, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37298, "sourceLowPrice": 1.36951}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49545, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "exitScreenshotUrl": "https://www.tradingview.com/x/2Vh1gYPu/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37298, "sourceLowPrice": 1.36951, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36991,7 +36991,7 @@
         <v>32</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782575547450</v>
+        <v>1782578952944</v>
       </c>
       <c r="BM70" t="n">
         <v>1.37313</v>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49546, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "exitScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36662, "sourceLowPrice": 1.36465}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49546, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "exitScreenshotUrl": "https://www.tradingview.com/x/QGlneXII/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36662, "sourceLowPrice": 1.36465, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37515,7 +37515,7 @@
         <v>32</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782575547451</v>
+        <v>1782578952944</v>
       </c>
       <c r="BM71" t="n">
         <v>1.36587</v>
@@ -37696,11 +37696,11 @@
       </c>
       <c r="DL71" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN71" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="EF71" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG71" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49547, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "exitScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36786, "sourceLowPrice": 1.36543}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49547, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "exitScreenshotUrl": "https://www.tradingview.com/x/apDASDyb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36786, "sourceLowPrice": 1.36543, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38039,7 +38039,7 @@
         <v>32</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782575547452</v>
+        <v>1782578952945</v>
       </c>
       <c r="BM72" t="n">
         <v>1.36453</v>
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49548, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "exitScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3682, "sourceLowPrice": 1.36696}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49548, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "exitScreenshotUrl": "https://www.tradingview.com/x/DLHf7u0k/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3682, "sourceLowPrice": 1.36696, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38563,7 +38563,7 @@
         <v>32</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782575547452</v>
+        <v>1782578952945</v>
       </c>
       <c r="BM73" t="n">
         <v>1.36747</v>
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49549, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "exitScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37174, "sourceLowPrice": 1.36737}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49549, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "exitScreenshotUrl": "https://www.tradingview.com/x/6rZC75zW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37174, "sourceLowPrice": 1.36737, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39087,7 +39087,7 @@
         <v>32</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782575547452</v>
+        <v>1782578952945</v>
       </c>
       <c r="BM74" t="n">
         <v>1.36666</v>
@@ -39556,7 +39556,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49550, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "exitScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36872, "sourceLowPrice": 1.36762}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49550, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "exitScreenshotUrl": "https://www.tradingview.com/x/xHjYqTTy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36872, "sourceLowPrice": 1.36762, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39611,7 +39611,7 @@
         <v>32</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782575547453</v>
+        <v>1782578952945</v>
       </c>
       <c r="BM75" t="n">
         <v>1.36781</v>
@@ -39805,7 +39805,7 @@
       </c>
       <c r="DO75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.36781, "new": 1.36769, "at": 1715253360000}]</t>
         </is>
       </c>
       <c r="DP75" t="n">
@@ -40080,7 +40080,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49552, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "exitScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36905, "sourceLowPrice": 1.36475}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49552, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "exitScreenshotUrl": "https://www.tradingview.com/x/iaVd1vWl/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36905, "sourceLowPrice": 1.36475, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40135,7 +40135,7 @@
         <v>32</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782575547454</v>
+        <v>1782578952946</v>
       </c>
       <c r="BM76" t="n">
         <v>1.36584</v>
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49553, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "exitScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36341, "sourceLowPrice": 1.36098}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49553, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "exitScreenshotUrl": "https://www.tradingview.com/x/9k9l6vKT/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36341, "sourceLowPrice": 1.36098, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40659,7 +40659,7 @@
         <v>32</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782575547454</v>
+        <v>1782578952946</v>
       </c>
       <c r="BM77" t="n">
         <v>1.36438</v>
@@ -41128,7 +41128,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49554, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "exitScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36221, "sourceLowPrice": 1.36068}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49554, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "exitScreenshotUrl": "https://www.tradingview.com/x/T6MmUhHv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36221, "sourceLowPrice": 1.36068, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41183,7 +41183,7 @@
         <v>32</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782575547454</v>
+        <v>1782578952946</v>
       </c>
       <c r="BM78" t="n">
         <v>1.36121</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49555, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "exitScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3627, "sourceLowPrice": 1.35961}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49555, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "exitScreenshotUrl": "https://www.tradingview.com/x/20pnKeBo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.3627, "sourceLowPrice": 1.35961, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41707,7 +41707,7 @@
         <v>32</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782575547455</v>
+        <v>1782578952946</v>
       </c>
       <c r="BM79" t="n">
         <v>1.36374</v>
@@ -41901,7 +41901,7 @@
       </c>
       <c r="DO79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.36374, "new": 1.36399, "at": 1716197340000}]</t>
         </is>
       </c>
       <c r="DP79" t="n">
@@ -42176,7 +42176,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49558, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "exitScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37173, "sourceLowPrice": 1.36522}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49558, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "exitScreenshotUrl": "https://www.tradingview.com/x/y2hYS7sr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37173, "sourceLowPrice": 1.36522, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42231,7 +42231,7 @@
         <v>32</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782575547455</v>
+        <v>1782578952947</v>
       </c>
       <c r="BM80" t="n">
         <v>1.36464</v>
@@ -42700,7 +42700,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49560, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "exitScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37134, "sourceLowPrice": 1.36702}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49560, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "exitScreenshotUrl": "https://www.tradingview.com/x/lgBj0CDj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.37134, "sourceLowPrice": 1.36702, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42755,7 +42755,7 @@
         <v>32</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782575547456</v>
+        <v>1782578952947</v>
       </c>
       <c r="BM81" t="n">
         <v>1.37276</v>
@@ -43224,7 +43224,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49561, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "exitScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36618, "sourceLowPrice": 1.36321}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49561, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "exitScreenshotUrl": "https://www.tradingview.com/x/of4jeLMA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36618, "sourceLowPrice": 1.36321, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43279,7 +43279,7 @@
         <v>32</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782575547456</v>
+        <v>1782578952947</v>
       </c>
       <c r="BM82" t="n">
         <v>1.36667</v>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49563, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "exitScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36506, "sourceLowPrice": 1.3619}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49563, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "exitScreenshotUrl": "https://www.tradingview.com/x/FwJLmnd7/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.36506, "sourceLowPrice": 1.3619, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43803,7 +43803,7 @@
         <v>32</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782575547457</v>
+        <v>1782578952947</v>
       </c>
       <c r="BM83" t="n">
         <v>1.36125</v>
@@ -43997,7 +43997,7 @@
       </c>
       <c r="DO83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.36125, "new": 1.36101, "at": 1716887700000}]</t>
         </is>
       </c>
       <c r="DP83" t="n">
@@ -44272,7 +44272,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49475, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "exitScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27972, "sourceLowPrice": 1.2756}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49475, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "exitScreenshotUrl": "https://www.tradingview.com/x/Js5eXjYM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27972, "sourceLowPrice": 1.2756, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44327,7 +44327,7 @@
         <v>32</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782575547457</v>
+        <v>1782578952947</v>
       </c>
       <c r="BM84" t="n">
         <v>1.27409</v>
@@ -44796,7 +44796,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49476, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "exitScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27954, "sourceLowPrice": 1.27836}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49476, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "exitScreenshotUrl": "https://www.tradingview.com/x/KhD74r4b/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27954, "sourceLowPrice": 1.27836, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44851,7 +44851,7 @@
         <v>32</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782575547458</v>
+        <v>1782578952948</v>
       </c>
       <c r="BM85" t="n">
         <v>1.27921</v>
@@ -45320,7 +45320,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49478, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "exitScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2778, "sourceLowPrice": 1.27624}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49478, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "exitScreenshotUrl": "https://www.tradingview.com/x/U36u3xtC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2778, "sourceLowPrice": 1.27624, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45375,7 +45375,7 @@
         <v>32</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782575547458</v>
+        <v>1782578952948</v>
       </c>
       <c r="BM86" t="n">
         <v>1.2764</v>
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49479, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28174, "sourceLowPrice": 1.27684}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49479, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/mrw2SlGZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28174, "sourceLowPrice": 1.27684, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45899,7 +45899,7 @@
         <v>32</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782575547459</v>
+        <v>1782578952948</v>
       </c>
       <c r="BM87" t="n">
         <v>1.27601</v>
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49480, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "exitScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27496, "sourceLowPrice": 1.27134}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49480, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "exitScreenshotUrl": "https://www.tradingview.com/x/KciKZSBj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27496, "sourceLowPrice": 1.27134, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46423,7 +46423,7 @@
         <v>32</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782575547460</v>
+        <v>1782578952949</v>
       </c>
       <c r="BM88" t="n">
         <v>1.27029</v>
@@ -46434,7 +46434,7 @@
         </is>
       </c>
       <c r="BO88" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="BP88" t="n">
         <v>2.88</v>
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49481, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "exitScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26807, "sourceLowPrice": 1.2669}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49481, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "exitScreenshotUrl": "https://www.tradingview.com/x/NRLneEGr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26807, "sourceLowPrice": 1.2669, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46947,7 +46947,7 @@
         <v>32</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782575547460</v>
+        <v>1782578952949</v>
       </c>
       <c r="BM89" t="n">
         <v>1.26765</v>
@@ -47416,7 +47416,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49482, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "exitScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27294, "sourceLowPrice": 1.26772}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49482, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "exitScreenshotUrl": "https://www.tradingview.com/x/bMdIVHui/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27294, "sourceLowPrice": 1.26772, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47471,7 +47471,7 @@
         <v>32</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782575547461</v>
+        <v>1782578952950</v>
       </c>
       <c r="BM90" t="n">
         <v>1.27424</v>
@@ -47940,7 +47940,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49564, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "exitScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27342, "sourceLowPrice": 1.26874}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49564, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "exitScreenshotUrl": "https://www.tradingview.com/x/KNWZYEcd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27342, "sourceLowPrice": 1.26874, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47995,7 +47995,7 @@
         <v>32</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782575547462</v>
+        <v>1782578952950</v>
       </c>
       <c r="BM91" t="n">
         <v>1.27425</v>
@@ -48176,11 +48176,11 @@
       </c>
       <c r="DL91" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN91" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
@@ -48464,7 +48464,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49565, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "exitScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26962, "sourceLowPrice": 1.26396}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49565, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "exitScreenshotUrl": "https://www.tradingview.com/x/wvsh3FKW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26962, "sourceLowPrice": 1.26396, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -48519,7 +48519,7 @@
         <v>32</v>
       </c>
       <c r="BL92" t="n">
-        <v>1782575547463</v>
+        <v>1782578952951</v>
       </c>
       <c r="BM92" t="n">
         <v>1.26985</v>
@@ -48988,7 +48988,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49566, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "exitScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26542, "sourceLowPrice": 1.26182}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49566, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "exitScreenshotUrl": "https://www.tradingview.com/x/6BnSuxSi/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26542, "sourceLowPrice": 1.26182, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -49043,7 +49043,7 @@
         <v>32</v>
       </c>
       <c r="BL93" t="n">
-        <v>1782575547464</v>
+        <v>1782578952951</v>
       </c>
       <c r="BM93" t="n">
         <v>1.26656</v>
@@ -49512,7 +49512,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49567, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "exitScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26708, "sourceLowPrice": 1.26466}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49567, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "exitScreenshotUrl": "https://www.tradingview.com/x/J1ZwFyEK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26708, "sourceLowPrice": 1.26466, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -49567,7 +49567,7 @@
         <v>32</v>
       </c>
       <c r="BL94" t="n">
-        <v>1782575547464</v>
+        <v>1782578952951</v>
       </c>
       <c r="BM94" t="n">
         <v>1.26364</v>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49568, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "exitScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2666, "sourceLowPrice": 1.26465}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49568, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "exitScreenshotUrl": "https://www.tradingview.com/x/DC5jzVin/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.2666, "sourceLowPrice": 1.26465, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -50091,7 +50091,7 @@
         <v>32</v>
       </c>
       <c r="BL95" t="n">
-        <v>1782575547464</v>
+        <v>1782578952951</v>
       </c>
       <c r="BM95" t="n">
         <v>1.26609</v>
@@ -50272,11 +50272,11 @@
       </c>
       <c r="DL95" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN95" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
       </c>
       <c r="EF95" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG95" t="inlineStr">
@@ -50560,7 +50560,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49569, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26553, "sourceLowPrice": 1.26198}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49569, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/onheK0OZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26553, "sourceLowPrice": 1.26198, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -50615,7 +50615,7 @@
         <v>32</v>
       </c>
       <c r="BL96" t="n">
-        <v>1782575547465</v>
+        <v>1782578952952</v>
       </c>
       <c r="BM96" t="n">
         <v>1.26671</v>
@@ -51084,7 +51084,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49570, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "exitScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.269, "sourceLowPrice": 1.26706}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49570, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "exitScreenshotUrl": "https://www.tradingview.com/x/XtGV8QyA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.269, "sourceLowPrice": 1.26706, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -51139,7 +51139,7 @@
         <v>32</v>
       </c>
       <c r="BL97" t="n">
-        <v>1782575547465</v>
+        <v>1782578952952</v>
       </c>
       <c r="BM97" t="n">
         <v>1.2683</v>
@@ -51608,7 +51608,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49571, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "exitScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26739, "sourceLowPrice": 1.26578}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49571, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "exitScreenshotUrl": "https://www.tradingview.com/x/7CTaemfO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26739, "sourceLowPrice": 1.26578, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -51663,7 +51663,7 @@
         <v>32</v>
       </c>
       <c r="BL98" t="n">
-        <v>1782575547466</v>
+        <v>1782578952952</v>
       </c>
       <c r="BM98" t="n">
         <v>1.26653</v>
@@ -52132,7 +52132,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49572, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26895, "sourceLowPrice": 1.267}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49572, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQziTjfH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.26895, "sourceLowPrice": 1.267, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -52187,7 +52187,7 @@
         <v>32</v>
       </c>
       <c r="BL99" t="n">
-        <v>1782575547467</v>
+        <v>1782578952953</v>
       </c>
       <c r="BM99" t="n">
         <v>1.26866</v>
@@ -52368,11 +52368,11 @@
       </c>
       <c r="DL99" t="inlineStr">
         <is>
-          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "haider 8.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN99" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
@@ -52656,7 +52656,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49573, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "exitScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27677, "sourceLowPrice": 1.27504}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49573, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "exitScreenshotUrl": "https://www.tradingview.com/x/UAmgfpRW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.27677, "sourceLowPrice": 1.27504, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -52711,7 +52711,7 @@
         <v>32</v>
       </c>
       <c r="BL100" t="n">
-        <v>1782575547468</v>
+        <v>1782578952953</v>
       </c>
       <c r="BM100" t="n">
         <v>1.27449</v>
@@ -53180,7 +53180,7 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 49574, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "exitScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28217, "sourceLowPrice": 1.27805}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 49574, "mentorFile": "haider 8.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "exitScreenshotUrl": "https://www.tradingview.com/x/ipG3jNwN/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.28217, "sourceLowPrice": 1.27805, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
@@ -53235,7 +53235,7 @@
         <v>32</v>
       </c>
       <c r="BL101" t="n">
-        <v>1782575547468</v>
+        <v>1782578952954</v>
       </c>
       <c r="BM101" t="n">
         <v>1.28269</v>
